--- a/saumilPractice_da.xlsx
+++ b/saumilPractice_da.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Saumil Data Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E089DD-36E1-4897-848A-C45917051247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36986FF-485B-4E0E-9343-DC6BE015713A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BAB2AD77-8422-4C69-A570-7A97D0F61326}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="294">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -903,6 +903,48 @@
   </si>
   <si>
     <t>vlookup withvalidation</t>
+  </si>
+  <si>
+    <t>hlookup</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>indexmatch club</t>
+  </si>
+  <si>
+    <t>unity</t>
+  </si>
+  <si>
+    <t>xlookup</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>Relative Reference</t>
+  </si>
+  <si>
+    <t>Mixed Refrence</t>
   </si>
 </sst>
 </file>
@@ -916,7 +958,7 @@
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -945,6 +987,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1031,10 +1080,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1091,6 +1141,9 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1100,12 +1153,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="32">
     <dxf>
@@ -1435,7 +1507,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7F3031C6-3F94-466C-A61D-A90D52859281}" name="Table410" displayName="Table410" ref="H86:K92" totalsRowCount="1">
   <autoFilter ref="H86:K91" xr:uid="{7F3031C6-3F94-466C-A61D-A90D52859281}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DDFF19FF-2AAF-496B-B0F4-403954456291}" name="product" totalsRowLabel="Total"/>
+    <tableColumn id="1" xr3:uid="{DDFF19FF-2AAF-496B-B0F4-403954456291}" name="product"/>
     <tableColumn id="2" xr3:uid="{41F80AE3-54F8-4956-A350-7ECA6F385BBA}" name="price ">
       <calculatedColumnFormula>VLOOKUP(H87,Table1[#All],4,0)</calculatedColumnFormula>
     </tableColumn>
@@ -3559,7 +3631,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B6CFF6-1F1C-45D8-B48F-5C94AFB1048F}">
-  <dimension ref="A1:S92"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -3572,20 +3644,20 @@
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3620,10 +3692,10 @@
       <c r="E3" s="2">
         <v>45</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -3708,7 +3780,7 @@
       <c r="R6" t="s">
         <v>2</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="34" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3747,7 +3819,7 @@
       <c r="R7">
         <v>86</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="34">
         <v>45</v>
       </c>
     </row>
@@ -3785,7 +3857,7 @@
       <c r="R8">
         <v>76</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="34">
         <v>40</v>
       </c>
     </row>
@@ -3819,7 +3891,7 @@
       <c r="R9">
         <v>65</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="34">
         <v>43</v>
       </c>
     </row>
@@ -3853,7 +3925,7 @@
       <c r="R10">
         <v>88</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="34">
         <v>35</v>
       </c>
     </row>
@@ -3876,7 +3948,7 @@
       <c r="R11">
         <v>75</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="34">
         <v>30</v>
       </c>
     </row>
@@ -3899,7 +3971,7 @@
       <c r="R12">
         <v>63</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="34">
         <v>38</v>
       </c>
     </row>
@@ -3908,7 +3980,7 @@
         <f>SUM(R7,R12)</f>
         <v>149</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="34">
         <f>SUM(S7:S12)</f>
         <v>231</v>
       </c>
@@ -3927,7 +3999,7 @@
         <f>AVERAGE(R7:R12)</f>
         <v>75.5</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="34">
         <f>AVERAGE(S7:S12)</f>
         <v>38.5</v>
       </c>
@@ -4042,7 +4114,7 @@
       <c r="G20" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="H20" s="30" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="4" t="s">
@@ -4070,7 +4142,7 @@
       <c r="Q20" s="3"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H21" s="29"/>
+      <c r="H21" s="30"/>
       <c r="I21" s="4" t="s">
         <v>1</v>
       </c>
@@ -4096,7 +4168,7 @@
       <c r="Q21" s="3"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H22" s="29"/>
+      <c r="H22" s="30"/>
       <c r="I22" s="4" t="s">
         <v>3</v>
       </c>
@@ -4122,7 +4194,7 @@
       <c r="Q22" s="3"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H23" s="29"/>
+      <c r="H23" s="30"/>
       <c r="I23" s="4" t="s">
         <v>2</v>
       </c>
@@ -4163,7 +4235,7 @@
       <c r="E24" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="29"/>
+      <c r="H24" s="30"/>
       <c r="I24" s="4" t="s">
         <v>14</v>
       </c>
@@ -4984,7 +5056,7 @@
       <c r="F62" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="G62" s="28">
+      <c r="G62" s="29">
         <v>45296</v>
       </c>
       <c r="H62" t="str">
@@ -5009,7 +5081,7 @@
       <c r="F63" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="G63" s="28">
+      <c r="G63" s="29">
         <v>45414</v>
       </c>
       <c r="H63" t="str">
@@ -5051,7 +5123,7 @@
       <c r="F65" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="G65" s="28">
+      <c r="G65" s="29">
         <v>45569</v>
       </c>
       <c r="H65" t="str">
@@ -5072,7 +5144,7 @@
       <c r="F66" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="G66" s="28">
+      <c r="G66" s="29">
         <v>45427</v>
       </c>
       <c r="H66" t="str">
@@ -5114,7 +5186,7 @@
       <c r="F68" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="G68" s="28">
+      <c r="G68" s="29">
         <v>45493</v>
       </c>
       <c r="H68" t="str">
@@ -5199,7 +5271,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C81" s="17" t="s">
         <v>264</v>
       </c>
@@ -5216,7 +5288,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82" spans="3:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C82" s="17" t="s">
         <v>266</v>
       </c>
@@ -5226,7 +5298,7 @@
       <c r="E82" s="17">
         <v>15</v>
       </c>
-      <c r="F82" s="31">
+      <c r="F82" s="33">
         <v>1299</v>
       </c>
       <c r="H82" t="s">
@@ -5242,7 +5314,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C83" s="17" t="s">
         <v>268</v>
       </c>
@@ -5271,7 +5343,7 @@
         <v>19485</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C84" s="17" t="s">
         <v>270</v>
       </c>
@@ -5284,12 +5356,12 @@
       <c r="F84" s="17">
         <v>699</v>
       </c>
-      <c r="P84">
-        <f>499*25</f>
-        <v>12475</v>
-      </c>
-    </row>
-    <row r="85" spans="3:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q84" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="R84" s="13"/>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C85" s="17" t="s">
         <v>272</v>
       </c>
@@ -5299,14 +5371,24 @@
       <c r="E85" s="17">
         <v>10</v>
       </c>
-      <c r="F85" s="31">
+      <c r="F85" s="33">
         <v>2499</v>
       </c>
       <c r="H85" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="Q85" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="R85" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="S85" s="36"/>
+      <c r="T85">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.25">
       <c r="H86" t="s">
         <v>275</v>
       </c>
@@ -5319,8 +5401,18 @@
       <c r="K86" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="Q86" t="s">
+        <v>288</v>
+      </c>
+      <c r="R86">
+        <v>80</v>
+      </c>
+      <c r="S86" s="35">
+        <f>R86/$T$85</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.25">
       <c r="H87" t="s">
         <v>264</v>
       </c>
@@ -5336,8 +5428,18 @@
         <f>PRODUCT(Table410[[#This Row],[price ]:[unit ]])</f>
         <v>12475</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="Q87" t="s">
+        <v>289</v>
+      </c>
+      <c r="R87">
+        <v>50</v>
+      </c>
+      <c r="S87" s="35">
+        <f t="shared" ref="S87:S89" si="7">R87/$T$85</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.25">
       <c r="H88" t="s">
         <v>266</v>
       </c>
@@ -5350,11 +5452,21 @@
         <v>15</v>
       </c>
       <c r="K88">
-        <f t="shared" ref="K88:K91" si="7">PRODUCT(I88:J88)</f>
+        <f t="shared" ref="K88:K91" si="8">PRODUCT(I88:J88)</f>
         <v>19485</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="Q88" t="s">
+        <v>290</v>
+      </c>
+      <c r="R88">
+        <v>60</v>
+      </c>
+      <c r="S88" s="35">
+        <f t="shared" si="7"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.25">
       <c r="H89" t="s">
         <v>268</v>
       </c>
@@ -5367,11 +5479,21 @@
         <v>30</v>
       </c>
       <c r="K89">
+        <f t="shared" si="8"/>
+        <v>26970</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>291</v>
+      </c>
+      <c r="R89">
+        <v>70</v>
+      </c>
+      <c r="S89" s="35">
         <f t="shared" si="7"/>
-        <v>26970</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.25">
       <c r="H90" t="s">
         <v>270</v>
       </c>
@@ -5384,34 +5506,426 @@
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13980</v>
       </c>
     </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="H91" t="s">
-        <v>272</v>
-      </c>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.25">
       <c r="I91">
-        <f>VLOOKUP(H91,Table1[#All],4,0)</f>
+        <f>VLOOKUP(H95,Table1[#All],4,0)</f>
         <v>2499</v>
       </c>
       <c r="J91">
-        <f>VLOOKUP(H91,Table1[#All],3,0)</f>
+        <f>VLOOKUP(H95,Table1[#All],3,0)</f>
         <v>10</v>
       </c>
       <c r="K91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24990</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="H92" t="s">
-        <v>61</v>
-      </c>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.25">
       <c r="K92">
         <f>SUBTOTAL(109,Table410[total])</f>
         <v>97900</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" s="28" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="C95" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="E95" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="F95" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="G95" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="H95" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="M95" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="O95"/>
+      <c r="S95" s="39"/>
+    </row>
+    <row r="96" spans="3:20" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="D96" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="E96" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="F96" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G96" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="H96" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="M96" s="37">
+        <v>1</v>
+      </c>
+      <c r="N96" s="37">
+        <v>2</v>
+      </c>
+      <c r="O96" s="37">
+        <v>3</v>
+      </c>
+      <c r="P96" s="37">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="37">
+        <v>5</v>
+      </c>
+      <c r="S96" s="38"/>
+    </row>
+    <row r="97" spans="3:19" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="D97" s="32">
+        <v>25</v>
+      </c>
+      <c r="E97" s="32">
+        <v>15</v>
+      </c>
+      <c r="F97" s="32">
+        <v>30</v>
+      </c>
+      <c r="G97" s="32">
+        <v>20</v>
+      </c>
+      <c r="H97" s="32">
+        <v>10</v>
+      </c>
+      <c r="M97" s="28">
+        <v>10</v>
+      </c>
+      <c r="N97" s="28">
+        <f>$M97*N$96</f>
+        <v>20</v>
+      </c>
+      <c r="O97" s="28">
+        <f t="shared" ref="O97:Q101" si="9">$M97*O$96</f>
+        <v>30</v>
+      </c>
+      <c r="P97" s="28">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+      <c r="Q97" s="28">
+        <f t="shared" si="9"/>
+        <v>50</v>
+      </c>
+      <c r="S97" s="39"/>
+    </row>
+    <row r="98" spans="3:19" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="D98" s="32">
+        <v>499</v>
+      </c>
+      <c r="E98" s="40">
+        <v>1299</v>
+      </c>
+      <c r="F98" s="32">
+        <v>899</v>
+      </c>
+      <c r="G98" s="32">
+        <v>699</v>
+      </c>
+      <c r="H98" s="40">
+        <v>2499</v>
+      </c>
+      <c r="M98" s="28">
+        <v>20</v>
+      </c>
+      <c r="N98" s="28">
+        <f t="shared" ref="N98:N101" si="10">$M98*N$96</f>
+        <v>40</v>
+      </c>
+      <c r="O98" s="28">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="P98" s="28">
+        <f t="shared" si="9"/>
+        <v>80</v>
+      </c>
+      <c r="Q98" s="28">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="S98" s="39"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="M99" s="28">
+        <v>30</v>
+      </c>
+      <c r="N99" s="28">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="O99" s="28">
+        <f t="shared" si="9"/>
+        <v>90</v>
+      </c>
+      <c r="P99" s="28">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="Q99" s="28">
+        <f t="shared" si="9"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C100" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="G100">
+        <f>INDEX(H87:K90,3,3)</f>
+        <v>30</v>
+      </c>
+      <c r="M100" s="28">
+        <v>40</v>
+      </c>
+      <c r="N100" s="28">
+        <f t="shared" si="10"/>
+        <v>80</v>
+      </c>
+      <c r="O100" s="28">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="P100" s="28">
+        <f t="shared" si="9"/>
+        <v>160</v>
+      </c>
+      <c r="Q100" s="28">
+        <f t="shared" si="9"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C101" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="D101" t="s">
+        <v>264</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="G101">
+        <f>MATCH(H88,H87:H90,0)</f>
+        <v>2</v>
+      </c>
+      <c r="L101" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="M101" s="28">
+        <v>50</v>
+      </c>
+      <c r="N101" s="28">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+      <c r="O101" s="28">
+        <f t="shared" si="9"/>
+        <v>150</v>
+      </c>
+      <c r="P101" s="28">
+        <f t="shared" si="9"/>
+        <v>200</v>
+      </c>
+      <c r="Q101" s="28">
+        <f t="shared" si="9"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C102" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D102">
+        <f>HLOOKUP(D101,C95:H98,4,0)</f>
+        <v>499</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="I102" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="L102" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="M102" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="N102" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="O102" s="13" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="103" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="F103" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="G103" t="str">
+        <f>INDEX(H86:H90,MATCH(I87,I86:I90,0))</f>
+        <v>Wireless Mouse</v>
+      </c>
+      <c r="H103">
+        <f t="shared" ref="H103:J103" si="11">INDEX(I86:I90,MATCH(J87,J86:J90,0))</f>
+        <v>499</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="11"/>
+        <v>25</v>
+      </c>
+      <c r="J103">
+        <f>INDEX(K86:K90,MATCH(K87,K86:K90,0))</f>
+        <v>12475</v>
+      </c>
+      <c r="L103" t="s">
+        <v>264</v>
+      </c>
+      <c r="M103">
+        <f>_xlfn.XLOOKUP(L103,H86:H90,I86:I90,"NA",0,1)</f>
+        <v>499</v>
+      </c>
+      <c r="N103">
+        <f t="shared" ref="N103:O106" si="12">_xlfn.XLOOKUP(M103,I86:I90,J86:J90,"NA",0,1)</f>
+        <v>25</v>
+      </c>
+      <c r="O103">
+        <f t="shared" si="12"/>
+        <v>12475</v>
+      </c>
+    </row>
+    <row r="104" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="G104" t="str">
+        <f t="shared" ref="G104:G107" si="13">INDEX(H87:H91,MATCH(I88,I87:I91,0))</f>
+        <v>Bluetooth Speaker</v>
+      </c>
+      <c r="H104">
+        <f t="shared" ref="H103:J106" si="14">INDEX(I87:I91,MATCH(J88,J87:J91,0))</f>
+        <v>1299</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="J104">
+        <f t="shared" ref="J104:J106" si="15">INDEX(K87:K91,MATCH(K88,K87:K91,0))</f>
+        <v>19485</v>
+      </c>
+      <c r="L104" t="s">
+        <v>266</v>
+      </c>
+      <c r="M104">
+        <f t="shared" ref="M104:M106" si="16">_xlfn.XLOOKUP(L104,H87:H91,I87:I91,"NA",0,1)</f>
+        <v>1299</v>
+      </c>
+      <c r="N104">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="O104">
+        <f t="shared" si="12"/>
+        <v>19485</v>
+      </c>
+    </row>
+    <row r="105" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="G105" t="str">
+        <f t="shared" si="13"/>
+        <v>Laptop Stand</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="14"/>
+        <v>899</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="15"/>
+        <v>26970</v>
+      </c>
+      <c r="L105" t="s">
+        <v>268</v>
+      </c>
+      <c r="M105">
+        <f t="shared" si="16"/>
+        <v>899</v>
+      </c>
+      <c r="N105">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="O105">
+        <f t="shared" si="12"/>
+        <v>26970</v>
+      </c>
+    </row>
+    <row r="106" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="G106" t="str">
+        <f t="shared" si="13"/>
+        <v>USB-C Charger</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="14"/>
+        <v>699</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="15"/>
+        <v>13980</v>
+      </c>
+      <c r="L106" t="s">
+        <v>270</v>
+      </c>
+      <c r="M106">
+        <f t="shared" si="16"/>
+        <v>699</v>
+      </c>
+      <c r="N106">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="O106">
+        <f t="shared" si="12"/>
+        <v>13980</v>
       </c>
     </row>
   </sheetData>
@@ -5459,7 +5973,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87:H91" xr:uid="{A61F504D-498D-4B2D-9A87-2FD881876D71}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H87:H90" xr:uid="{A61F504D-498D-4B2D-9A87-2FD881876D71}">
       <formula1>$C$81:$C$85</formula1>
     </dataValidation>
   </dataValidations>
